--- a/outputs/55085.xlsx
+++ b/outputs/55085.xlsx
@@ -408,7 +408,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
@@ -431,139 +434,139 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="4" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="3" borderId="6" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="6" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="7" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="9" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -769,7 +772,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="1" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J1" s="2" t="e">
         <f aca="false">#ref!</f>
         <v>#NAME?</v>
@@ -783,7 +786,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G2" s="3" t="s">
         <v>0</v>
       </c>
@@ -803,7 +806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G3" s="4" t="s">
         <v>3</v>
       </c>
@@ -827,85 +830,85 @@
         <v>Bhadra</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="G4" s="6"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="G5" s="6"/>
       <c r="J5" s="6"/>
     </row>
-    <row r="6" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="G6" s="6"/>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="G7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="G8" s="6"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="G10" s="6" t="n">
-        <f aca="false">INDEX('Master-RM'!$I$12:$K$20,MATCH(G2,'Master-RM'!$A$12:$A$20,0),IF(G3="Shrawan",1,3))</f>
+        <f aca="false">INDEX('Master-RM'!$I$8:$I$20,MATCH($G$2,'Master-RM'!$A$8:$A$20,0))</f>
         <v>202</v>
       </c>
       <c r="H10" s="6" t="n">
-        <f aca="false">INDEX('Master-RM'!$I$12:$K$20,MATCH(H2,'Master-RM'!$A$12:$A$20,0),IF(H3="Shrawan",1,3))</f>
+        <f aca="false">INDEX('Master-RM'!$I$8:$I$20,MATCH($H$2,'Master-RM'!$A$8:$A$20,0))</f>
         <v>137</v>
       </c>
       <c r="I10" s="6" t="n">
-        <f aca="false">INDEX('Master-RM'!$I$12:$K$20,MATCH(I2,'Master-RM'!$A$12:$A$20,0),IF(I3="Shrawan",1,3))</f>
+        <f aca="false">INDEX('Master-RM'!$I$8:$I$20,MATCH($I$2,'Master-RM'!$A$8:$A$20,0))</f>
         <v>155</v>
       </c>
       <c r="J10" s="6" t="n">
-        <f aca="false">INDEX('Master-RM'!$I$12:$K$20,MATCH(J2,'Master-RM'!$A$12:$A$20,0),IF(J3="Shrawan",1,3))</f>
+        <f aca="false">INDEX('Master-RM'!$K$8:$K$20,MATCH($J$2,'Master-RM'!$A$8:$A$20,0))</f>
         <v>439</v>
       </c>
       <c r="K10" s="6" t="n">
-        <f aca="false">INDEX('Master-RM'!$I$12:$K$20,MATCH(K2,'Master-RM'!$A$12:$A$20,0),IF(K3="Shrawan",1,3))</f>
+        <f aca="false">INDEX('Master-RM'!$K$8:$K$20,MATCH($K$2,'Master-RM'!$A$8:$A$20,0))</f>
         <v>376</v>
       </c>
       <c r="L10" s="6" t="n">
-        <f aca="false">INDEX('Master-RM'!$I$12:$K$20,MATCH(L2,'Master-RM'!$A$12:$A$20,0),IF(L3="Shrawan",1,3))</f>
+        <f aca="false">INDEX('Master-RM'!$K$8:$K$20,MATCH($L$2,'Master-RM'!$A$8:$A$20,0))</f>
         <v>721</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
     </row>
-    <row r="12" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
     </row>
-    <row r="13" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -945,7 +948,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="11" min="8" style="9" width="16.71"/>
   </cols>
   <sheetData>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H5" s="10" t="s">
         <v>6</v>
       </c>
@@ -962,7 +965,7 @@
         <v>Net Purchase</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
       <c r="D6" s="13" t="s">
@@ -1019,7 +1022,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19"/>
       <c r="C8" s="20"/>
       <c r="D8" s="21"/>
@@ -1031,7 +1034,7 @@
       <c r="J8" s="20"/>
       <c r="K8" s="20"/>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="23" t="s">
         <v>13</v>
       </c>
@@ -1054,7 +1057,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="23" t="s">
         <v>14</v>
       </c>
@@ -1077,7 +1080,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="23" t="s">
         <v>15</v>
       </c>
@@ -1100,7 +1103,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
         <v>0</v>
       </c>
@@ -1138,10 +1141,10 @@
         <v>439</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="30"/>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="23" t="s">
         <v>17</v>
       </c>
@@ -1165,7 +1168,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="23" t="s">
         <v>18</v>
       </c>
@@ -1188,7 +1191,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
         <v>1</v>
       </c>
@@ -1217,10 +1220,10 @@
         <v>376</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="32"/>
     </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="33" t="s">
         <v>19</v>
       </c>
@@ -1243,7 +1246,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="34" t="s">
         <v>20</v>
       </c>
@@ -1266,7 +1269,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
         <v>2</v>
       </c>
@@ -1294,10 +1297,10 @@
         <v>721</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="30"/>
     </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="30"/>
     </row>
   </sheetData>
